--- a/Testes/reescala/Teste seleção e cruzamento/Teste4/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste seleção e cruzamento/Teste4/3_melhor_escala.xlsx
@@ -793,8 +793,8 @@
       <c r="AH2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" s="5" t="n">
-        <v>0</v>
+      <c r="AI2" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -901,8 +901,8 @@
       <c r="AG3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" s="4" t="n">
-        <v>1</v>
+      <c r="AH3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI3" s="5" t="n">
         <v>0</v>
@@ -1012,11 +1012,11 @@
       <c r="AG4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="4" t="n">
-        <v>1</v>
+      <c r="AH4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1048,11 +1048,11 @@
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>1</v>
+      <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
@@ -1069,17 +1069,17 @@
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>1</v>
+      <c r="P5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>0</v>
@@ -1099,8 +1099,8 @@
       <c r="Y5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="5" t="n">
-        <v>0</v>
+      <c r="Z5" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="5" t="n">
         <v>0</v>
@@ -1111,11 +1111,11 @@
       <c r="AC5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="4" t="n">
-        <v>1</v>
+      <c r="AD5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AF5" s="5" t="n">
         <v>0</v>
@@ -1126,8 +1126,8 @@
       <c r="AH5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" s="5" t="n">
-        <v>0</v>
+      <c r="AI5" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1186,14 +1186,14 @@
       <c r="Q6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0</v>
+      <c r="R6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="5" t="n">
         <v>0</v>
@@ -1288,11 +1288,11 @@
       <c r="N7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>1</v>
+      <c r="O7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1393,8 +1393,8 @@
       <c r="L8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="5" t="n">
-        <v>0</v>
+      <c r="M8" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>0</v>
@@ -1441,14 +1441,14 @@
       <c r="AB8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="5" t="n">
-        <v>0</v>
+      <c r="AC8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AF8" s="5" t="n">
         <v>0</v>
@@ -1489,14 +1489,14 @@
       <c r="G9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0</v>
+      <c r="H9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
@@ -1510,8 +1510,8 @@
       <c r="N9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="5" t="n">
-        <v>0</v>
+      <c r="O9" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="P9" s="5" t="n">
         <v>0</v>
@@ -1627,17 +1627,17 @@
       <c r="P10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>1</v>
+      <c r="Q10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="U10" s="5" t="n">
         <v>0</v>
@@ -1762,8 +1762,8 @@
       <c r="X11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" s="5" t="n">
-        <v>0</v>
+      <c r="Y11" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Z11" s="5" t="n">
         <v>0</v>
@@ -1849,20 +1849,20 @@
       <c r="P12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="4" t="n">
-        <v>1</v>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0</v>
+      <c r="S12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V12" s="5" t="n">
         <v>0</v>
@@ -1885,8 +1885,8 @@
       <c r="AB12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AC12" s="5" t="n">
-        <v>0</v>
+      <c r="AC12" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AD12" s="5" t="n">
         <v>0</v>
@@ -1960,14 +1960,14 @@
       <c r="P13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>1</v>
+      <c r="Q13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="T13" s="5" t="n">
         <v>0</v>
@@ -2005,8 +2005,8 @@
       <c r="AE13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF13" s="5" t="n">
-        <v>0</v>
+      <c r="AF13" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AG13" s="5" t="n">
         <v>0</v>
@@ -2113,20 +2113,20 @@
       <c r="AD14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" s="5" t="n">
-        <v>0</v>
+      <c r="AE14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2152,17 +2152,17 @@
       <c r="F15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="5" t="n">
-        <v>0</v>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>1</v>
+      <c r="I15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
@@ -2236,8 +2236,8 @@
       <c r="AH15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" s="5" t="n">
-        <v>0</v>
+      <c r="AI15" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2323,11 +2323,11 @@
       <c r="Z16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AA16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="4" t="n">
-        <v>1</v>
+      <c r="AA16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AC16" s="5" t="n">
         <v>0</v>
@@ -2437,11 +2437,11 @@
       <c r="AA17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="4" t="n">
-        <v>1</v>
+      <c r="AB17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AD17" s="5" t="n">
         <v>0</v>
@@ -2458,8 +2458,8 @@
       <c r="AH17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" s="5" t="n">
-        <v>0</v>
+      <c r="AI17" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2602,20 +2602,20 @@
       <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>0</v>
+      <c r="I19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
         <v>0</v>
@@ -2719,14 +2719,14 @@
       <c r="J20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
+      <c r="K20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>0</v>
@@ -2743,11 +2743,11 @@
       <c r="R20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="4" t="n">
-        <v>1</v>
+      <c r="S20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="U20" s="5" t="n">
         <v>0</v>
@@ -2818,8 +2818,8 @@
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>0</v>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0</v>
@@ -2875,11 +2875,11 @@
       <c r="Y21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="4" t="n">
-        <v>1</v>
+      <c r="Z21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AB21" s="5" t="n">
         <v>0</v>
@@ -2902,8 +2902,8 @@
       <c r="AH21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" s="5" t="n">
-        <v>0</v>
+      <c r="AI21" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2956,11 +2956,11 @@
       <c r="O22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>0</v>
+      <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R22" s="5" t="n">
         <v>0</v>
@@ -3112,11 +3112,11 @@
       <c r="AD23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="4" t="n">
-        <v>1</v>
+      <c r="AE23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AG23" s="5" t="n">
         <v>0</v>
@@ -3187,14 +3187,14 @@
       <c r="R24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="5" t="n">
-        <v>0</v>
+      <c r="S24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V24" s="5" t="n">
         <v>0</v>
@@ -3223,11 +3223,11 @@
       <c r="AD24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="4" t="n">
-        <v>1</v>
+      <c r="AE24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AG24" s="5" t="n">
         <v>0</v>
@@ -3262,11 +3262,11 @@
       <c r="F25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>1</v>
+      <c r="G25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       <c r="O25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="5" t="n">
-        <v>0</v>
+      <c r="P25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R25" s="5" t="n">
         <v>0</v>
@@ -3379,11 +3379,11 @@
       <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>1</v>
+      <c r="I26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0</v>
@@ -3400,8 +3400,8 @@
       <c r="O26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
+      <c r="P26" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
@@ -3436,17 +3436,17 @@
       <c r="AA26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AB26" s="5" t="n">
-        <v>0</v>
+      <c r="AB26" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AC26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE26" s="5" t="n">
-        <v>0</v>
+      <c r="AD26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AF26" s="5" t="n">
         <v>0</v>
@@ -3484,8 +3484,8 @@
       <c r="F27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="5" t="n">
-        <v>0</v>
+      <c r="G27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
@@ -3529,14 +3529,14 @@
       <c r="U27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" s="5" t="n">
-        <v>0</v>
+      <c r="V27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Y27" s="5" t="n">
         <v>0</v>
@@ -3559,17 +3559,17 @@
       <c r="AE27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF27" s="5" t="n">
-        <v>0</v>
+      <c r="AF27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AG27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI27" s="5" t="n">
-        <v>0</v>
+      <c r="AH27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3616,8 +3616,8 @@
       <c r="M28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="5" t="n">
-        <v>0</v>
+      <c r="N28" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="O28" s="5" t="n">
         <v>0</v>
@@ -3625,17 +3625,17 @@
       <c r="P28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" s="5" t="n">
-        <v>0</v>
+      <c r="Q28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="U28" s="5" t="n">
         <v>0</v>
@@ -3715,11 +3715,11 @@
       <c r="I29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>1</v>
+      <c r="J29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="L29" s="5" t="n">
         <v>0</v>
@@ -3742,11 +3742,11 @@
       <c r="R29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>1</v>
+      <c r="S29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="U29" s="5" t="n">
         <v>0</v>
@@ -3757,23 +3757,23 @@
       <c r="W29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="5" t="n">
-        <v>0</v>
+      <c r="X29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AD29" s="5" t="n">
         <v>0</v>
@@ -3856,14 +3856,14 @@
       <c r="S30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>1</v>
+      <c r="T30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="W30" s="5" t="n">
         <v>0</v>
@@ -3880,29 +3880,29 @@
       <c r="AA30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AB30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD30" s="5" t="n">
-        <v>0</v>
+      <c r="AB30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AE30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="4" t="n">
-        <v>1</v>
+      <c r="AF30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI30" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3958,8 +3958,8 @@
       <c r="P31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="5" t="n">
-        <v>0</v>
+      <c r="Q31" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R31" s="5" t="n">
         <v>0</v>
@@ -3970,11 +3970,11 @@
       <c r="T31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" s="5" t="n">
-        <v>0</v>
+      <c r="U31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="W31" s="5" t="n">
         <v>0</v>
@@ -3988,32 +3988,32 @@
       <c r="Z31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AA31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI31" s="5" t="n">
-        <v>0</v>
+      <c r="AA31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -4075,11 +4075,11 @@
       <c r="R32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="4" t="n">
-        <v>1</v>
+      <c r="S32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="U32" s="5" t="n">
         <v>0</v>
@@ -4102,17 +4102,17 @@
       <c r="AA32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AB32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="4" t="n">
-        <v>1</v>
+      <c r="AB32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AF32" s="5" t="n">
         <v>0</v>
@@ -4198,44 +4198,44 @@
       <c r="V33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" s="4" t="n">
-        <v>1</v>
+      <c r="W33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Y33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="4" t="n">
-        <v>1</v>
+      <c r="Z33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4300,23 +4300,23 @@
       <c r="S34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="4" t="n">
-        <v>1</v>
+      <c r="T34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Z34" s="5" t="n">
         <v>0</v>
@@ -4333,11 +4333,11 @@
       <c r="AD34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="5" t="n">
-        <v>0</v>
+      <c r="AE34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AG34" s="5" t="n">
         <v>0</v>
@@ -4414,14 +4414,14 @@
       <c r="T35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" s="5" t="n">
-        <v>0</v>
+      <c r="U35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X35" s="5" t="n">
         <v>0</v>
@@ -4432,20 +4432,20 @@
       <c r="Z35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AA35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE35" s="5" t="n">
-        <v>0</v>
+      <c r="AA35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AF35" s="5" t="n">
         <v>0</v>
@@ -4486,26 +4486,26 @@
       <c r="G36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>1</v>
+      <c r="H36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="5" t="n">
-        <v>0</v>
+      <c r="K36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>1</v>
+      <c r="M36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="O36" s="5" t="n">
         <v>0</v>
@@ -4522,11 +4522,11 @@
       <c r="S36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" s="5" t="n">
-        <v>0</v>
+      <c r="T36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V36" s="5" t="n">
         <v>0</v>
@@ -4561,11 +4561,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -4633,32 +4633,32 @@
       <c r="S37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="5" t="n">
-        <v>0</v>
+      <c r="T37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="W37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="5" t="n">
-        <v>0</v>
+      <c r="X37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AC37" s="5" t="n">
         <v>0</v>
@@ -4708,8 +4708,8 @@
       <c r="G38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="5" t="n">
-        <v>0</v>
+      <c r="H38" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>0</v>
@@ -4726,8 +4726,8 @@
       <c r="M38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="5" t="n">
-        <v>0</v>
+      <c r="N38" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="O38" s="5" t="n">
         <v>0</v>
@@ -4744,50 +4744,50 @@
       <c r="S38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="4" t="n">
-        <v>1</v>
+      <c r="T38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH38" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI38" s="5" t="n">
         <v>0</v>
@@ -4849,20 +4849,20 @@
       <c r="Q39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" s="5" t="n">
-        <v>0</v>
+      <c r="R39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="W39" s="5" t="n">
         <v>0</v>
@@ -4897,11 +4897,11 @@
       <c r="AG39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="4" t="n">
-        <v>1</v>
+      <c r="AH39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI39" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4927,11 +4927,11 @@
       <c r="F40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>0</v>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>0</v>
@@ -4942,11 +4942,11 @@
       <c r="K40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>0</v>
@@ -5050,11 +5050,11 @@
       <c r="J41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>1</v>
+      <c r="K41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0</v>
@@ -5065,11 +5065,11 @@
       <c r="O41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="4" t="n">
-        <v>1</v>
+      <c r="P41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R41" s="5" t="n">
         <v>0</v>
@@ -5095,29 +5095,29 @@
       <c r="Y41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD41" s="5" t="n">
-        <v>0</v>
+      <c r="Z41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AE41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG41" s="5" t="n">
-        <v>0</v>
+      <c r="AF41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AH41" s="5" t="n">
         <v>0</v>
@@ -5170,8 +5170,8 @@
       <c r="M42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N42" s="5" t="n">
-        <v>0</v>
+      <c r="N42" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="O42" s="5" t="n">
         <v>0</v>
@@ -5188,53 +5188,53 @@
       <c r="S42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI42" s="5" t="n">
-        <v>0</v>
+      <c r="T42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -5302,14 +5302,14 @@
       <c r="T43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U43" s="4" t="n">
-        <v>1</v>
+      <c r="U43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="V43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="5" t="n">
-        <v>0</v>
+      <c r="W43" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X43" s="5" t="n">
         <v>0</v>
@@ -5332,20 +5332,20 @@
       <c r="AD43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI43" s="5" t="n">
-        <v>0</v>
+      <c r="AE43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -5401,8 +5401,8 @@
       <c r="P44" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" s="5" t="n">
-        <v>0</v>
+      <c r="Q44" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R44" s="4" t="n">
         <v>1</v>
@@ -5410,11 +5410,11 @@
       <c r="S44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" s="5" t="n">
-        <v>0</v>
+      <c r="T44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V44" s="5" t="n">
         <v>0</v>
@@ -5449,14 +5449,14 @@
       <c r="AF44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI44" s="5" t="n">
-        <v>0</v>
+      <c r="AG44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -5509,14 +5509,14 @@
       <c r="O45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" s="5" t="n">
-        <v>0</v>
+      <c r="P45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="S45" s="5" t="n">
         <v>0</v>
@@ -5536,11 +5536,11 @@
       <c r="X45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="5" t="n">
-        <v>0</v>
+      <c r="Y45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="5" t="n">
         <v>0</v>
@@ -5557,17 +5557,17 @@
       <c r="AE45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" s="4" t="n">
-        <v>1</v>
+      <c r="AF45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI45" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5614,11 +5614,11 @@
       <c r="M46" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>1</v>
+      <c r="N46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P46" s="5" t="n">
         <v>0</v>
@@ -5650,20 +5650,20 @@
       <c r="Y46" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD46" s="5" t="n">
-        <v>0</v>
+      <c r="Z46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AE46" s="5" t="n">
         <v>0</v>
@@ -5704,11 +5704,11 @@
       <c r="F47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>1</v>
+      <c r="G47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>0</v>
@@ -5719,17 +5719,17 @@
       <c r="K47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v>1</v>
+      <c r="L47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P47" s="5" t="n">
         <v>0</v>
@@ -5746,50 +5746,50 @@
       <c r="T47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" s="4" t="n">
-        <v>1</v>
+      <c r="U47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI47" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5896,8 +5896,8 @@
       <c r="AG48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH48" s="4" t="n">
-        <v>1</v>
+      <c r="AH48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI48" s="5" t="n">
         <v>0</v>
@@ -5935,8 +5935,8 @@
       <c r="I49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="5" t="n">
-        <v>0</v>
+      <c r="J49" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="K49" s="5" t="n">
         <v>0</v>
@@ -5944,17 +5944,17 @@
       <c r="L49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v>1</v>
+      <c r="M49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q49" s="5" t="n">
         <v>0</v>
@@ -5971,32 +5971,32 @@
       <c r="U49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X49" s="5" t="n">
-        <v>0</v>
+      <c r="V49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Y49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="4" t="n">
-        <v>1</v>
+      <c r="Z49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AE49" s="5" t="n">
         <v>0</v>
@@ -6034,11 +6034,11 @@
       <c r="E50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0</v>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>0</v>
@@ -6079,11 +6079,11 @@
       <c r="T50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" s="5" t="n">
-        <v>0</v>
+      <c r="U50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="W50" s="5" t="n">
         <v>0</v>
@@ -6100,17 +6100,17 @@
       <c r="AA50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AB50" s="5" t="n">
-        <v>0</v>
+      <c r="AB50" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AC50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE50" s="5" t="n">
-        <v>0</v>
+      <c r="AD50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AF50" s="5" t="n">
         <v>0</v>
@@ -6121,8 +6121,8 @@
       <c r="AH50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI50" s="5" t="n">
-        <v>0</v>
+      <c r="AI50" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -6202,8 +6202,8 @@
       <c r="X51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y51" s="5" t="n">
-        <v>0</v>
+      <c r="Y51" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Z51" s="5" t="n">
         <v>0</v>
@@ -6214,8 +6214,8 @@
       <c r="AB51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AC51" s="5" t="n">
-        <v>0</v>
+      <c r="AC51" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AD51" s="5" t="n">
         <v>0</v>
@@ -6301,23 +6301,23 @@
       <c r="T52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z52" s="5" t="n">
-        <v>0</v>
+      <c r="U52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="5" t="n">
         <v>0</v>
@@ -6334,14 +6334,14 @@
       <c r="AE52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH52" s="5" t="n">
-        <v>0</v>
+      <c r="AF52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI52" s="5" t="n">
         <v>0</v>
